--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C07E9A63-810A-4C20-BB97-E91A2938B7C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C858289-DA99-4736-A015-83F9B0441643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="117">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -386,6 +386,9 @@
   </si>
   <si>
     <t>13-09-2026</t>
+  </si>
+  <si>
+    <t>14-09-2026</t>
   </si>
 </sst>
 </file>
@@ -2595,26 +2598,50 @@
       <c r="N37" s="17"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="B38" s="14">
+        <v>480</v>
+      </c>
+      <c r="C38" s="14">
+        <v>60</v>
+      </c>
+      <c r="D38" s="14">
+        <v>240</v>
+      </c>
+      <c r="E38" s="14">
+        <v>120</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>180</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N38" s="16" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="13"/>
@@ -10625,7 +10652,7 @@
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401 N38" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C858289-DA99-4736-A015-83F9B0441643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A991904-04C2-485E-8279-40A9E9049EB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="117">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="13">
-        <v>46304</v>
+        <v>46274</v>
       </c>
       <c r="B34" s="14">
         <v>480</v>
@@ -2463,7 +2463,7 @@
     </row>
     <row r="35" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A35" s="13">
-        <v>46335</v>
+        <v>46304</v>
       </c>
       <c r="B35" s="14">
         <v>480</v>
@@ -2478,21 +2478,21 @@
         <v>90</v>
       </c>
       <c r="F35" s="14">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="G35" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H35" s="14">
         <v>180</v>
       </c>
       <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v>1130</v>
+        <v>1380</v>
       </c>
       <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v>310</v>
+        <v>60</v>
       </c>
       <c r="K35" s="16" t="s">
         <v>105</v>
@@ -2509,7 +2509,7 @@
     </row>
     <row r="36" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A36" s="13">
-        <v>46365</v>
+        <v>46335</v>
       </c>
       <c r="B36" s="14">
         <v>480</v>
@@ -2554,8 +2554,8 @@
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A37" s="13" t="s">
-        <v>115</v>
+      <c r="A37" s="13">
+        <v>46365</v>
       </c>
       <c r="B37" s="14">
         <v>480</v>
@@ -2599,7 +2599,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B38" s="14">
         <v>480</v>
@@ -2639,31 +2639,53 @@
       <c r="M38" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="N38" s="16" t="s">
+      <c r="N38" s="16"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A39" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="B39" s="14">
+        <v>480</v>
+      </c>
+      <c r="C39" s="14">
+        <v>60</v>
+      </c>
+      <c r="D39" s="14">
+        <v>240</v>
+      </c>
+      <c r="E39" s="14">
+        <v>90</v>
+      </c>
+      <c r="F39" s="14">
+        <v>150</v>
+      </c>
+      <c r="G39" s="14">
+        <v>3</v>
+      </c>
+      <c r="H39" s="14">
+        <v>200</v>
+      </c>
+      <c r="I39" s="15">
+        <f t="shared" si="0"/>
+        <v>1220</v>
+      </c>
+      <c r="J39" s="15">
+        <f t="shared" si="1"/>
+        <v>220</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M39" s="16" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+      <c r="N39" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A991904-04C2-485E-8279-40A9E9049EB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EEA81E3-34CF-45B2-B585-127E50475B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="119">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -389,6 +389,12 @@
   </si>
   <si>
     <t>14-09-2026</t>
+  </si>
+  <si>
+    <t>15-09-2026</t>
+  </si>
+  <si>
+    <t>Today is my Python CA and it wa very good . I faced a little bit dificulty but overall its nice.</t>
   </si>
 </sst>
 </file>
@@ -2687,27 +2693,51 @@
         <v>87</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+    <row r="40" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="B40" s="14">
+        <v>480</v>
+      </c>
+      <c r="C40" s="14">
+        <v>70</v>
+      </c>
+      <c r="D40" s="14">
+        <v>250</v>
+      </c>
+      <c r="E40" s="14">
+        <v>120</v>
+      </c>
+      <c r="F40" s="14">
+        <v>350</v>
+      </c>
+      <c r="G40" s="14">
+        <v>5</v>
+      </c>
+      <c r="H40" s="14">
+        <v>170</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EEA81E3-34CF-45B2-B585-127E50475B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2059241-DE89-480B-8FF2-4CC9D07EC7CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="121">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -395,6 +395,12 @@
   </si>
   <si>
     <t>Today is my Python CA and it wa very good . I faced a little bit dificulty but overall its nice.</t>
+  </si>
+  <si>
+    <t>16-09-2026</t>
+  </si>
+  <si>
+    <t>17-09-2026</t>
   </si>
 </sst>
 </file>
@@ -2710,7 +2716,7 @@
         <v>120</v>
       </c>
       <c r="F40" s="14">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="G40" s="14">
         <v>5</v>
@@ -2720,11 +2726,11 @@
       </c>
       <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v>1440</v>
+        <v>1340</v>
       </c>
       <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K40" s="16" t="s">
         <v>105</v>
@@ -2740,47 +2746,91 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="B41" s="14">
+        <v>480</v>
+      </c>
+      <c r="C41" s="14">
+        <v>90</v>
+      </c>
+      <c r="D41" s="14">
+        <v>240</v>
+      </c>
+      <c r="E41" s="14">
+        <v>120</v>
+      </c>
+      <c r="F41" s="14">
+        <v>200</v>
+      </c>
+      <c r="G41" s="14">
+        <v>4</v>
+      </c>
+      <c r="H41" s="14">
+        <v>120</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
+        <v>190</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>78</v>
+      </c>
       <c r="N41" s="17"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="A42" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="B42" s="14">
+        <v>480</v>
+      </c>
+      <c r="C42" s="14">
+        <v>90</v>
+      </c>
+      <c r="D42" s="14">
+        <v>200</v>
+      </c>
+      <c r="E42" s="14">
+        <v>120</v>
+      </c>
+      <c r="F42" s="14">
+        <v>350</v>
+      </c>
+      <c r="G42" s="14">
+        <v>7</v>
+      </c>
+      <c r="H42" s="14">
+        <v>120</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1360</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
+        <v>80</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>78</v>
+      </c>
       <c r="N42" s="17"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.35">

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2059241-DE89-480B-8FF2-4CC9D07EC7CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DBDE843-1722-4C3B-B89B-66422CBE9FA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="123">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -401,6 +401,12 @@
   </si>
   <si>
     <t>17-09-2026</t>
+  </si>
+  <si>
+    <t>18-09-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today is my first Hackathon and I enjoyed it very much. Also learn a lot of things and it’s a very great experience. </t>
   </si>
 </sst>
 </file>
@@ -2833,27 +2839,51 @@
       </c>
       <c r="N42" s="17"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+    <row r="43" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A43" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="B43" s="14">
+        <v>480</v>
+      </c>
+      <c r="C43" s="14">
+        <v>90</v>
+      </c>
+      <c r="D43" s="14">
+        <v>240</v>
+      </c>
+      <c r="E43" s="14">
+        <v>120</v>
+      </c>
+      <c r="F43" s="14">
+        <v>0</v>
+      </c>
+      <c r="G43" s="14">
+        <v>0</v>
+      </c>
+      <c r="H43" s="14">
+        <v>120</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DBDE843-1722-4C3B-B89B-66422CBE9FA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16CD4D2C-F5E8-41A3-9EF3-2D7D0078BF37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="125">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -407,6 +407,12 @@
   </si>
   <si>
     <t xml:space="preserve">Today is my first Hackathon and I enjoyed it very much. Also learn a lot of things and it’s a very great experience. </t>
+  </si>
+  <si>
+    <t>19-09-2026</t>
+  </si>
+  <si>
+    <t>Hackathon is going on till 6 pm today.</t>
   </si>
 </sst>
 </file>
@@ -2853,7 +2859,7 @@
         <v>240</v>
       </c>
       <c r="E43" s="14">
-        <v>120</v>
+        <v>320</v>
       </c>
       <c r="F43" s="14">
         <v>0</v>
@@ -2866,11 +2872,11 @@
       </c>
       <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v>1050</v>
+        <v>1250</v>
       </c>
       <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v>390</v>
+        <v>190</v>
       </c>
       <c r="K43" s="16" t="s">
         <v>105</v>
@@ -2885,27 +2891,51 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+    <row r="44" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A44" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="B44" s="14">
+        <v>480</v>
+      </c>
+      <c r="C44" s="14">
+        <v>70</v>
+      </c>
+      <c r="D44" s="14">
+        <v>200</v>
+      </c>
+      <c r="E44" s="14">
+        <v>300</v>
+      </c>
+      <c r="F44" s="14">
+        <v>0</v>
+      </c>
+      <c r="G44" s="14">
+        <v>0</v>
+      </c>
+      <c r="H44" s="14">
+        <v>150</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>240</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16CD4D2C-F5E8-41A3-9EF3-2D7D0078BF37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15E87193-FFCB-4166-8616-B10D8F8CE17D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="126">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -413,6 +413,9 @@
   </si>
   <si>
     <t>Hackathon is going on till 6 pm today.</t>
+  </si>
+  <si>
+    <t>20-09-2026</t>
   </si>
 </sst>
 </file>
@@ -2938,25 +2941,47 @@
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="B45" s="14">
+        <v>480</v>
+      </c>
+      <c r="C45" s="14">
+        <v>60</v>
+      </c>
+      <c r="D45" s="14">
+        <v>200</v>
+      </c>
+      <c r="E45" s="14">
+        <v>240</v>
+      </c>
+      <c r="F45" s="14">
+        <v>0</v>
+      </c>
+      <c r="G45" s="14">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14">
+        <v>200</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
+        <v>260</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>78</v>
+      </c>
       <c r="N45" s="17"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.35">

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15E87193-FFCB-4166-8616-B10D8F8CE17D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A241C61F-8C02-48B0-8A17-62B967D8EC3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="128">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -416,6 +416,12 @@
   </si>
   <si>
     <t>20-09-2026</t>
+  </si>
+  <si>
+    <t>21-09-2026</t>
+  </si>
+  <si>
+    <t>Today I got to know my CA marks of networking and it was average ,due to lack of time I was not able to complete the test.</t>
   </si>
 </sst>
 </file>
@@ -2984,27 +2990,51 @@
       </c>
       <c r="N45" s="17"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+    <row r="46" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A46" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="B46" s="14">
+        <v>480</v>
+      </c>
+      <c r="C46" s="14">
+        <v>60</v>
+      </c>
+      <c r="D46" s="14">
+        <v>220</v>
+      </c>
+      <c r="E46" s="14">
+        <v>200</v>
+      </c>
+      <c r="F46" s="14">
+        <v>150</v>
+      </c>
+      <c r="G46" s="14">
+        <v>3</v>
+      </c>
+      <c r="H46" s="14">
+        <v>180</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>150</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A241C61F-8C02-48B0-8A17-62B967D8EC3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41955C23-FB94-4108-BD6A-E39CA80FA451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="130">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -367,9 +367,6 @@
     <t>Very good</t>
   </si>
   <si>
-    <t xml:space="preserve">Today I regestered for heckathon </t>
-  </si>
-  <si>
     <t>Preparing for heckathon as well as for CA.</t>
   </si>
   <si>
@@ -394,9 +391,6 @@
     <t>15-09-2026</t>
   </si>
   <si>
-    <t>Today is my Python CA and it wa very good . I faced a little bit dificulty but overall its nice.</t>
-  </si>
-  <si>
     <t>16-09-2026</t>
   </si>
   <si>
@@ -422,6 +416,18 @@
   </si>
   <si>
     <t>Today I got to know my CA marks of networking and it was average ,due to lack of time I was not able to complete the test.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today I registred for heckathon </t>
+  </si>
+  <si>
+    <t>Today is my Python CA and it was very good . I faced a little bit dificulty but overall its nice.</t>
+  </si>
+  <si>
+    <t>22-09-2026</t>
+  </si>
+  <si>
+    <t>Today also I got to know CA marks of analytical skill and it was not so good due to the problem held during exam.</t>
   </si>
 </sst>
 </file>
@@ -2224,7 +2230,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="13">
         <v>46121</v>
       </c>
@@ -2267,7 +2273,7 @@
         <v>78</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="29" x14ac:dyDescent="0.35">
@@ -2313,7 +2319,7 @@
         <v>78</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
@@ -2394,7 +2400,7 @@
         <v>170</v>
       </c>
       <c r="K32" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L32" s="16" t="s">
         <v>74</v>
@@ -2447,7 +2453,7 @@
         <v>78</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
@@ -2537,7 +2543,7 @@
         <v>78</v>
       </c>
       <c r="N35" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="29" x14ac:dyDescent="0.35">
@@ -2583,7 +2589,7 @@
         <v>78</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
@@ -2632,7 +2638,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B38" s="14">
         <v>480</v>
@@ -2676,7 +2682,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B39" s="14">
         <v>480</v>
@@ -2722,7 +2728,7 @@
     </row>
     <row r="40" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A40" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B40" s="14">
         <v>480</v>
@@ -2763,12 +2769,12 @@
         <v>78</v>
       </c>
       <c r="N40" s="17" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" s="13" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B41" s="14">
         <v>480</v>
@@ -2812,7 +2818,7 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" s="13" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B42" s="14">
         <v>480</v>
@@ -2856,7 +2862,7 @@
     </row>
     <row r="43" spans="1:14" ht="58" x14ac:dyDescent="0.35">
       <c r="A43" s="13" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B43" s="14">
         <v>480</v>
@@ -2897,12 +2903,12 @@
         <v>78</v>
       </c>
       <c r="N43" s="17" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" s="13" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B44" s="14">
         <v>480</v>
@@ -2943,12 +2949,12 @@
         <v>78</v>
       </c>
       <c r="N44" s="17" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" s="13" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B45" s="14">
         <v>480</v>
@@ -2992,7 +2998,7 @@
     </row>
     <row r="46" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A46" s="13" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B46" s="14">
         <v>480</v>
@@ -3033,30 +3039,54 @@
         <v>78</v>
       </c>
       <c r="N46" s="17" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A47" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B47" s="14">
+        <v>480</v>
+      </c>
+      <c r="C47" s="14">
+        <v>60</v>
+      </c>
+      <c r="D47" s="14">
+        <v>180</v>
+      </c>
+      <c r="E47" s="14">
+        <v>120</v>
+      </c>
+      <c r="F47" s="14">
+        <v>350</v>
+      </c>
+      <c r="G47" s="14">
+        <v>7</v>
+      </c>
+      <c r="H47" s="14">
+        <v>160</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
+        <v>90</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41955C23-FB94-4108-BD6A-E39CA80FA451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F37CA3EC-F9B9-4BF2-B929-E1B34551DF15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="132">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -428,6 +428,12 @@
   </si>
   <si>
     <t>Today also I got to know CA marks of analytical skill and it was not so good due to the problem held during exam.</t>
+  </si>
+  <si>
+    <t>23-09-2026</t>
+  </si>
+  <si>
+    <t>Today I missed one class.</t>
   </si>
 </sst>
 </file>
@@ -3089,26 +3095,50 @@
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="B48" s="14">
+        <v>480</v>
+      </c>
+      <c r="C48" s="14">
+        <v>70</v>
+      </c>
+      <c r="D48" s="14">
+        <v>200</v>
+      </c>
+      <c r="E48" s="14">
+        <v>180</v>
+      </c>
+      <c r="F48" s="14">
+        <v>150</v>
+      </c>
+      <c r="G48" s="14">
+        <v>3</v>
+      </c>
+      <c r="H48" s="14">
+        <v>180</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
+        <v>180</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F37CA3EC-F9B9-4BF2-B929-E1B34551DF15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5768BCA0-5465-4A1B-B6E7-292FE2194CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="134">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -434,6 +434,12 @@
   </si>
   <si>
     <t>Today I missed one class.</t>
+  </si>
+  <si>
+    <t>24-09-2026</t>
+  </si>
+  <si>
+    <t>It’s a very nice day bright sunny and highly energetic.</t>
   </si>
 </sst>
 </file>
@@ -3140,27 +3146,51 @@
         <v>131</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+    <row r="49" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A49" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B49" s="14">
+        <v>420</v>
+      </c>
+      <c r="C49" s="14">
+        <v>60</v>
+      </c>
+      <c r="D49" s="14">
+        <v>200</v>
+      </c>
+      <c r="E49" s="14">
+        <v>220</v>
+      </c>
+      <c r="F49" s="14">
+        <v>350</v>
+      </c>
+      <c r="G49" s="14">
+        <v>7</v>
+      </c>
+      <c r="H49" s="14">
+        <v>120</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
+        <v>70</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5768BCA0-5465-4A1B-B6E7-292FE2194CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11927637-1E14-4FE1-B78E-BC8ACEAFEC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="135">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -440,6 +440,9 @@
   </si>
   <si>
     <t>It’s a very nice day bright sunny and highly energetic.</t>
+  </si>
+  <si>
+    <t>25-09-2026</t>
   </si>
 </sst>
 </file>
@@ -3193,25 +3196,47 @@
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+      <c r="A50" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="B50" s="14">
+        <v>480</v>
+      </c>
+      <c r="C50" s="14">
+        <v>70</v>
+      </c>
+      <c r="D50" s="14">
+        <v>180</v>
+      </c>
+      <c r="E50" s="14">
+        <v>180</v>
+      </c>
+      <c r="F50" s="14">
+        <v>200</v>
+      </c>
+      <c r="G50" s="14">
+        <v>4</v>
+      </c>
+      <c r="H50" s="14">
+        <v>150</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
+        <v>180</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>78</v>
+      </c>
       <c r="N50" s="17"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.35">

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11927637-1E14-4FE1-B78E-BC8ACEAFEC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC30F2C-FC1E-4F24-B4C1-8F7DDCACBEC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="137">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -443,6 +443,12 @@
   </si>
   <si>
     <t>25-09-2026</t>
+  </si>
+  <si>
+    <t>26-09-2026</t>
+  </si>
+  <si>
+    <t>Today i worked on my python minor project.</t>
   </si>
 </sst>
 </file>
@@ -3163,7 +3169,7 @@
         <v>200</v>
       </c>
       <c r="E49" s="14">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="F49" s="14">
         <v>350</v>
@@ -3172,15 +3178,15 @@
         <v>7</v>
       </c>
       <c r="H49" s="14">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v>1370</v>
+        <v>1390</v>
       </c>
       <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="K49" s="16" t="s">
         <v>105</v>
@@ -3239,27 +3245,51 @@
       </c>
       <c r="N50" s="17"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+    <row r="51" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A51" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="B51" s="14">
+        <v>480</v>
+      </c>
+      <c r="C51" s="14">
+        <v>70</v>
+      </c>
+      <c r="D51" s="14">
+        <v>200</v>
+      </c>
+      <c r="E51" s="14">
+        <v>250</v>
+      </c>
+      <c r="F51" s="14">
+        <v>0</v>
+      </c>
+      <c r="G51" s="14">
+        <v>0</v>
+      </c>
+      <c r="H51" s="14">
+        <v>220</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
+        <v>220</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC30F2C-FC1E-4F24-B4C1-8F7DDCACBEC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53BFFB70-8D33-4BE7-85B3-FBABC9843156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="147">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -449,6 +449,36 @@
   </si>
   <si>
     <t>Today i worked on my python minor project.</t>
+  </si>
+  <si>
+    <t>27-09-2026</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>moderate</t>
+  </si>
+  <si>
+    <t>Due to protest I feel disturbed.</t>
+  </si>
+  <si>
+    <t>28-09-2026</t>
+  </si>
+  <si>
+    <t>I travelled  home as per instructions given by university.</t>
+  </si>
+  <si>
+    <t>29-09-2026</t>
+  </si>
+  <si>
+    <t>It’s a lovely day because after a long time I met my family .</t>
+  </si>
+  <si>
+    <t>30-09-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preparing for Mid term examination. </t>
   </si>
 </sst>
 </file>
@@ -2117,7 +2147,7 @@
     </row>
     <row r="26" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A26" s="13">
-        <v>46031</v>
+        <v>46266</v>
       </c>
       <c r="B26" s="14">
         <v>480</v>
@@ -2163,7 +2193,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="13">
-        <v>46062</v>
+        <v>46267</v>
       </c>
       <c r="B27" s="14">
         <v>480</v>
@@ -2207,7 +2237,7 @@
     </row>
     <row r="28" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A28" s="13">
-        <v>46090</v>
+        <v>46268</v>
       </c>
       <c r="B28" s="14">
         <v>480</v>
@@ -2253,7 +2283,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="13">
-        <v>46121</v>
+        <v>46269</v>
       </c>
       <c r="B29" s="14">
         <v>480</v>
@@ -2299,7 +2329,7 @@
     </row>
     <row r="30" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="13">
-        <v>46151</v>
+        <v>46270</v>
       </c>
       <c r="B30" s="14">
         <v>480</v>
@@ -2345,7 +2375,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="13">
-        <v>46182</v>
+        <v>46271</v>
       </c>
       <c r="B31" s="14">
         <v>480</v>
@@ -2389,7 +2419,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="13">
-        <v>46212</v>
+        <v>46272</v>
       </c>
       <c r="B32" s="14">
         <v>480</v>
@@ -2433,7 +2463,7 @@
     </row>
     <row r="33" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A33" s="13">
-        <v>46243</v>
+        <v>46273</v>
       </c>
       <c r="B33" s="14">
         <v>480</v>
@@ -2523,7 +2553,7 @@
     </row>
     <row r="35" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A35" s="13">
-        <v>46304</v>
+        <v>46275</v>
       </c>
       <c r="B35" s="14">
         <v>480</v>
@@ -2569,7 +2599,7 @@
     </row>
     <row r="36" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A36" s="13">
-        <v>46335</v>
+        <v>46276</v>
       </c>
       <c r="B36" s="14">
         <v>480</v>
@@ -2615,7 +2645,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="13">
-        <v>46365</v>
+        <v>46277</v>
       </c>
       <c r="B37" s="14">
         <v>480</v>
@@ -3292,92 +3322,188 @@
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+      <c r="A52" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="B52" s="14">
+        <v>420</v>
+      </c>
+      <c r="C52" s="14">
+        <v>60</v>
+      </c>
+      <c r="D52" s="14">
+        <v>200</v>
+      </c>
+      <c r="E52" s="14">
+        <v>120</v>
+      </c>
+      <c r="F52" s="14">
+        <v>0</v>
+      </c>
+      <c r="G52" s="14">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14">
+        <v>220</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+        <v>420</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A53" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="B53" s="14">
+        <v>480</v>
+      </c>
+      <c r="C53" s="14">
+        <v>70</v>
+      </c>
+      <c r="D53" s="14">
+        <v>200</v>
+      </c>
+      <c r="E53" s="14">
+        <v>90</v>
+      </c>
+      <c r="F53" s="14">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>350</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+        <v>250</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A54" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="B54" s="14">
+        <v>480</v>
+      </c>
+      <c r="C54" s="14">
+        <v>60</v>
+      </c>
+      <c r="D54" s="14">
+        <v>220</v>
+      </c>
+      <c r="E54" s="14">
+        <v>120</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>220</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+        <v>340</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A55" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="B55" s="14">
+        <v>480</v>
+      </c>
+      <c r="C55" s="14">
+        <v>70</v>
+      </c>
+      <c r="D55" s="14">
+        <v>300</v>
+      </c>
+      <c r="E55" s="14">
+        <v>180</v>
+      </c>
+      <c r="F55" s="14">
+        <v>0</v>
+      </c>
+      <c r="G55" s="14">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14">
+        <v>180</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
+        <v>230</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53BFFB70-8D33-4BE7-85B3-FBABC9843156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC83D04B-CF87-444F-A996-8104D327401E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="148">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -479,6 +479,9 @@
   </si>
   <si>
     <t xml:space="preserve">Preparing for Mid term examination. </t>
+  </si>
+  <si>
+    <t>Busy in household tasks.</t>
   </si>
 </sst>
 </file>
@@ -3506,70 +3509,140 @@
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="A56" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B56" s="14">
+        <v>480</v>
+      </c>
+      <c r="C56" s="14">
+        <v>60</v>
+      </c>
+      <c r="D56" s="14">
+        <v>250</v>
+      </c>
+      <c r="E56" s="14">
+        <v>220</v>
+      </c>
+      <c r="F56" s="14">
+        <v>0</v>
+      </c>
+      <c r="G56" s="14">
+        <v>0</v>
+      </c>
+      <c r="H56" s="14">
+        <v>180</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
+        <v>250</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>78</v>
+      </c>
       <c r="N56" s="17"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+    <row r="57" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A57" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B57" s="14">
+        <v>480</v>
+      </c>
+      <c r="C57" s="14">
+        <v>60</v>
+      </c>
+      <c r="D57" s="14">
+        <v>300</v>
+      </c>
+      <c r="E57" s="14">
+        <v>180</v>
+      </c>
+      <c r="F57" s="14">
+        <v>0</v>
+      </c>
+      <c r="G57" s="14">
+        <v>0</v>
+      </c>
+      <c r="H57" s="14">
+        <v>220</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
+        <v>200</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+      <c r="A58" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B58" s="14">
+        <v>480</v>
+      </c>
+      <c r="C58" s="14">
+        <v>60</v>
+      </c>
+      <c r="D58" s="14">
+        <v>320</v>
+      </c>
+      <c r="E58" s="14">
+        <v>200</v>
+      </c>
+      <c r="F58" s="14">
+        <v>0</v>
+      </c>
+      <c r="G58" s="14">
+        <v>0</v>
+      </c>
+      <c r="H58" s="14">
+        <v>300</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>1360</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
+        <v>80</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC83D04B-CF87-444F-A996-8104D327401E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1072855B-1C7E-4A78-A998-8EFD678024EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="149">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -482,6 +482,9 @@
   </si>
   <si>
     <t>Busy in household tasks.</t>
+  </si>
+  <si>
+    <t>Today is my birthday but nothing happened special. Its as usual as everyday.</t>
   </si>
 </sst>
 </file>
@@ -3644,27 +3647,51 @@
         <v>147</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
+    <row r="59" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A59" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B59" s="14">
+        <v>480</v>
+      </c>
+      <c r="C59" s="14">
+        <v>60</v>
+      </c>
+      <c r="D59" s="14">
+        <v>350</v>
+      </c>
+      <c r="E59" s="14">
+        <v>220</v>
+      </c>
+      <c r="F59" s="14">
+        <v>0</v>
+      </c>
+      <c r="G59" s="14">
+        <v>0</v>
+      </c>
+      <c r="H59" s="14">
+        <v>280</v>
+      </c>
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="17"/>
+        <v>50</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1072855B-1C7E-4A78-A998-8EFD678024EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2118779B-9C67-4B20-8F2A-CA3A2D7891B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="149">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3694,25 +3694,47 @@
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
+      <c r="A60" s="13">
+        <v>46300</v>
+      </c>
+      <c r="B60" s="14">
+        <v>480</v>
+      </c>
+      <c r="C60" s="14">
+        <v>70</v>
+      </c>
+      <c r="D60" s="14">
+        <v>320</v>
+      </c>
+      <c r="E60" s="14">
+        <v>200</v>
+      </c>
+      <c r="F60" s="14">
+        <v>0</v>
+      </c>
+      <c r="G60" s="14">
+        <v>0</v>
+      </c>
+      <c r="H60" s="14">
+        <v>250</v>
+      </c>
+      <c r="I60" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J60" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
+        <v>120</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>78</v>
+      </c>
       <c r="N60" s="17"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.35">

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2118779B-9C67-4B20-8F2A-CA3A2D7891B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA3BCF52-3595-485C-83B0-74F33524F8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="150">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -485,6 +485,9 @@
   </si>
   <si>
     <t>Today is my birthday but nothing happened special. Its as usual as everyday.</t>
+  </si>
+  <si>
+    <t>Taking online classes.</t>
   </si>
 </sst>
 </file>
@@ -3704,27 +3707,27 @@
         <v>70</v>
       </c>
       <c r="D60" s="14">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="E60" s="14">
         <v>200</v>
       </c>
       <c r="F60" s="14">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G60" s="14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H60" s="14">
         <v>250</v>
       </c>
       <c r="I60" s="15">
         <f t="shared" si="0"/>
-        <v>1320</v>
+        <v>1350</v>
       </c>
       <c r="J60" s="15">
         <f t="shared" si="1"/>
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="K60" s="16" t="s">
         <v>105</v>
@@ -3738,26 +3741,50 @@
       <c r="N60" s="17"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
+      <c r="A61" s="13">
+        <v>46301</v>
+      </c>
+      <c r="B61" s="14">
+        <v>480</v>
+      </c>
+      <c r="C61" s="14">
+        <v>60</v>
+      </c>
+      <c r="D61" s="14">
+        <v>220</v>
+      </c>
+      <c r="E61" s="14">
+        <v>120</v>
+      </c>
+      <c r="F61" s="14">
+        <v>350</v>
+      </c>
+      <c r="G61" s="14">
+        <v>7</v>
+      </c>
+      <c r="H61" s="14">
+        <v>100</v>
+      </c>
+      <c r="I61" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J61" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="17"/>
+        <v>110</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N61" s="17" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA3BCF52-3595-485C-83B0-74F33524F8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A453B80-0F47-4CDF-B92B-9BB8D92B0D33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="150">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3787,47 +3787,91 @@
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
+      <c r="A62" s="13">
+        <v>46302</v>
+      </c>
+      <c r="B62" s="14">
+        <v>480</v>
+      </c>
+      <c r="C62" s="14">
+        <v>60</v>
+      </c>
+      <c r="D62" s="14">
+        <v>250</v>
+      </c>
+      <c r="E62" s="14">
+        <v>150</v>
+      </c>
+      <c r="F62" s="14">
+        <v>200</v>
+      </c>
+      <c r="G62" s="14">
+        <v>4</v>
+      </c>
+      <c r="H62" s="14">
+        <v>200</v>
+      </c>
+      <c r="I62" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>1340</v>
+      </c>
+      <c r="J62" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
+        <v>100</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>78</v>
+      </c>
       <c r="N62" s="17"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
+      <c r="A63" s="13">
+        <v>46303</v>
+      </c>
+      <c r="B63" s="14">
+        <v>420</v>
+      </c>
+      <c r="C63" s="14">
+        <v>60</v>
+      </c>
+      <c r="D63" s="14">
+        <v>350</v>
+      </c>
+      <c r="E63" s="14">
+        <v>240</v>
+      </c>
+      <c r="F63" s="14">
+        <v>0</v>
+      </c>
+      <c r="G63" s="14">
+        <v>0</v>
+      </c>
+      <c r="H63" s="14">
+        <v>220</v>
+      </c>
+      <c r="I63" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J63" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
+        <v>150</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N63" s="17"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.35">

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A453B80-0F47-4CDF-B92B-9BB8D92B0D33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A69DEC86-D736-409B-8852-04CB08CE5B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="152">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -488,6 +488,12 @@
   </si>
   <si>
     <t>Taking online classes.</t>
+  </si>
+  <si>
+    <t>Travelling back to university.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Its raining and the weather is stunning. </t>
   </si>
 </sst>
 </file>
@@ -3875,70 +3881,142 @@
       <c r="N63" s="17"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
+      <c r="A64" s="13">
+        <v>46304</v>
+      </c>
+      <c r="B64" s="14">
+        <v>420</v>
+      </c>
+      <c r="C64" s="14">
+        <v>60</v>
+      </c>
+      <c r="D64" s="14">
+        <v>180</v>
+      </c>
+      <c r="E64" s="14">
+        <v>90</v>
+      </c>
+      <c r="F64" s="14">
+        <v>0</v>
+      </c>
+      <c r="G64" s="14">
+        <v>0</v>
+      </c>
+      <c r="H64" s="14">
+        <v>540</v>
+      </c>
+      <c r="I64" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J64" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="17"/>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15" t="str">
+        <v>150</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="N64" s="17" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A65" s="13">
+        <v>46305</v>
+      </c>
+      <c r="B65" s="14">
+        <v>480</v>
+      </c>
+      <c r="C65" s="14">
+        <v>60</v>
+      </c>
+      <c r="D65" s="14">
+        <v>300</v>
+      </c>
+      <c r="E65" s="14">
+        <v>120</v>
+      </c>
+      <c r="F65" s="14">
+        <v>0</v>
+      </c>
+      <c r="G65" s="14">
+        <v>0</v>
+      </c>
+      <c r="H65" s="14">
+        <v>200</v>
+      </c>
+      <c r="I65" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J65" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
-      <c r="N65" s="17"/>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A66" s="13"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15" t="str">
+        <v>280</v>
+      </c>
+      <c r="K65" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N65" s="17" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A66" s="13">
+        <v>46306</v>
+      </c>
+      <c r="B66" s="14">
+        <v>480</v>
+      </c>
+      <c r="C66" s="14">
+        <v>60</v>
+      </c>
+      <c r="D66" s="14">
+        <v>300</v>
+      </c>
+      <c r="E66" s="14">
+        <v>200</v>
+      </c>
+      <c r="F66" s="14">
+        <v>0</v>
+      </c>
+      <c r="G66" s="14">
+        <v>0</v>
+      </c>
+      <c r="H66" s="14">
+        <v>180</v>
+      </c>
+      <c r="I66" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J66" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
-      <c r="N66" s="17"/>
+        <v>220</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N66" s="17" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A69DEC86-D736-409B-8852-04CB08CE5B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37A18214-3356-46B7-8755-01CFC0B2EEAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="153">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -494,6 +494,9 @@
   </si>
   <si>
     <t xml:space="preserve">Its raining and the weather is stunning. </t>
+  </si>
+  <si>
+    <t>Today is my mid term examination.</t>
   </si>
 </sst>
 </file>
@@ -4018,27 +4021,51 @@
         <v>151</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A67" s="13"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="15" t="str">
+    <row r="67" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A67" s="13">
+        <v>46307</v>
+      </c>
+      <c r="B67" s="14">
+        <v>480</v>
+      </c>
+      <c r="C67" s="14">
+        <v>60</v>
+      </c>
+      <c r="D67" s="14">
+        <v>320</v>
+      </c>
+      <c r="E67" s="14">
+        <v>180</v>
+      </c>
+      <c r="F67" s="14">
+        <v>0</v>
+      </c>
+      <c r="G67" s="14">
+        <v>0</v>
+      </c>
+      <c r="H67" s="14">
+        <v>200</v>
+      </c>
+      <c r="I67" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="15" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J67" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="16"/>
-      <c r="N67" s="17"/>
+        <v>200</v>
+      </c>
+      <c r="K67" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="L67" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M67" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="N67" s="17" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37A18214-3356-46B7-8755-01CFC0B2EEAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87ECC43E-8056-49C3-87AA-F2A889798450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,15 +30,12 @@
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="164">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -226,9 +223,6 @@
     <t>15-08-2026</t>
   </si>
   <si>
-    <t>NOTE</t>
-  </si>
-  <si>
     <t>Moderate</t>
   </si>
   <si>
@@ -497,6 +491,42 @@
   </si>
   <si>
     <t>Today is my mid term examination.</t>
+  </si>
+  <si>
+    <t>NOTES</t>
+  </si>
+  <si>
+    <t>Today is also my mid term examination.</t>
+  </si>
+  <si>
+    <t>Feeling not good due to cold and fewer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verygood </t>
+  </si>
+  <si>
+    <t>Today is my holiday and I helped my friend to sell his product because he is an MBA student and its their CA</t>
+  </si>
+  <si>
+    <t>Due to fewer I am not feeling well.</t>
+  </si>
+  <si>
+    <t>Today is my last exam.</t>
+  </si>
+  <si>
+    <t>Feeling unwell dueto fewer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After a long break today is my classes and its a new energy with a new starting. </t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Today i went to central library and there is very calm enviornment which helps me to concentrate more on my study.</t>
+  </si>
+  <si>
+    <t>Today sir gave us CA of C++ and its also like python project.</t>
   </si>
 </sst>
 </file>
@@ -635,7 +665,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -679,6 +709,21 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1272,7 +1317,7 @@
         <v>47</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>62</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
@@ -1417,21 +1462,21 @@
         <v>210</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L9" s="16" t="s">
         <v>59</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B10" s="14">
         <v>420</v>
@@ -1463,21 +1508,21 @@
         <v>330</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L10" s="16" t="s">
         <v>59</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B11" s="14">
         <v>540</v>
@@ -1509,21 +1554,21 @@
         <v>420</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L11" s="16" t="s">
         <v>58</v>
       </c>
       <c r="M11" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N11" s="17" t="s">
         <v>69</v>
-      </c>
-      <c r="N11" s="17" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B12" s="14">
         <v>480</v>
@@ -1564,12 +1609,12 @@
         <v>49</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B13" s="14">
         <v>480</v>
@@ -1604,18 +1649,18 @@
         <v>48</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M13" s="16" t="s">
         <v>49</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B14" s="14">
         <v>480</v>
@@ -1647,21 +1692,21 @@
         <v>140</v>
       </c>
       <c r="K14" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M14" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="L14" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="M14" s="16" t="s">
+      <c r="N14" s="17" t="s">
         <v>78</v>
-      </c>
-      <c r="N14" s="17" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A15" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B15" s="14">
         <v>480</v>
@@ -1696,18 +1741,18 @@
         <v>48</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M15" s="16" t="s">
         <v>49</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B16" s="14">
         <v>480</v>
@@ -1739,21 +1784,21 @@
         <v>380</v>
       </c>
       <c r="K16" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="L16" s="16" t="s">
         <v>83</v>
-      </c>
-      <c r="L16" s="16" t="s">
-        <v>84</v>
       </c>
       <c r="M16" s="16" t="s">
         <v>49</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B17" s="14">
         <v>480</v>
@@ -1791,15 +1836,15 @@
         <v>58</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B18" s="14">
         <v>480</v>
@@ -1834,18 +1879,18 @@
         <v>60</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B19" s="14">
         <v>480</v>
@@ -1880,18 +1925,18 @@
         <v>48</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M19" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B20" s="14">
         <v>480</v>
@@ -1929,15 +1974,15 @@
         <v>58</v>
       </c>
       <c r="M20" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B21" s="14">
         <v>480</v>
@@ -1969,21 +2014,21 @@
         <v>50</v>
       </c>
       <c r="K21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M21" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="L21" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="M21" s="16" t="s">
+      <c r="N21" s="17" t="s">
         <v>96</v>
-      </c>
-      <c r="N21" s="17" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B22" s="14">
         <v>480</v>
@@ -2015,21 +2060,21 @@
         <v>240</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M22" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="N22" s="17" t="s">
         <v>78</v>
-      </c>
-      <c r="N22" s="17" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B23" s="14">
         <v>480</v>
@@ -2067,15 +2112,15 @@
         <v>58</v>
       </c>
       <c r="M23" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B24" s="14">
         <v>480</v>
@@ -2113,15 +2158,15 @@
         <v>58</v>
       </c>
       <c r="M24" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B25" s="14">
         <v>480</v>
@@ -2156,10 +2201,10 @@
         <v>48</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M25" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N25" s="17"/>
     </row>
@@ -2197,16 +2242,16 @@
         <v>80</v>
       </c>
       <c r="K26" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="N26" s="17" t="s">
         <v>105</v>
-      </c>
-      <c r="L26" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="M26" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="N26" s="17" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
@@ -2246,10 +2291,10 @@
         <v>48</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M27" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N27" s="17"/>
     </row>
@@ -2287,16 +2332,16 @@
         <v>60</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L28" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M28" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
@@ -2333,16 +2378,16 @@
         <v>90</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M29" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="29" x14ac:dyDescent="0.35">
@@ -2379,16 +2424,16 @@
         <v>390</v>
       </c>
       <c r="K30" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L30" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M30" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
@@ -2428,10 +2473,10 @@
         <v>60</v>
       </c>
       <c r="L31" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M31" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N31" s="17"/>
     </row>
@@ -2469,13 +2514,13 @@
         <v>170</v>
       </c>
       <c r="K32" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L32" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M32" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N32" s="17"/>
     </row>
@@ -2513,16 +2558,16 @@
         <v>40</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L33" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M33" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
@@ -2559,13 +2604,13 @@
         <v>230</v>
       </c>
       <c r="K34" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L34" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M34" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N34" s="17"/>
     </row>
@@ -2603,16 +2648,16 @@
         <v>60</v>
       </c>
       <c r="K35" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L35" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M35" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N35" s="17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="29" x14ac:dyDescent="0.35">
@@ -2649,16 +2694,16 @@
         <v>110</v>
       </c>
       <c r="K36" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L36" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M36" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
@@ -2695,19 +2740,19 @@
         <v>360</v>
       </c>
       <c r="K37" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L37" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M37" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N37" s="17"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B38" s="14">
         <v>480</v>
@@ -2739,19 +2784,19 @@
         <v>360</v>
       </c>
       <c r="K38" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L38" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M38" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N38" s="16"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B39" s="14">
         <v>480</v>
@@ -2783,21 +2828,21 @@
         <v>220</v>
       </c>
       <c r="K39" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L39" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M39" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N39" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A40" s="13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B40" s="14">
         <v>480</v>
@@ -2829,21 +2874,21 @@
         <v>100</v>
       </c>
       <c r="K40" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L40" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M40" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N40" s="17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B41" s="14">
         <v>480</v>
@@ -2875,19 +2920,19 @@
         <v>190</v>
       </c>
       <c r="K41" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L41" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M41" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N41" s="17"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B42" s="14">
         <v>480</v>
@@ -2919,19 +2964,19 @@
         <v>80</v>
       </c>
       <c r="K42" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L42" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M42" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N42" s="17"/>
     </row>
     <row r="43" spans="1:14" ht="58" x14ac:dyDescent="0.35">
       <c r="A43" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B43" s="14">
         <v>480</v>
@@ -2963,21 +3008,21 @@
         <v>190</v>
       </c>
       <c r="K43" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L43" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M43" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N43" s="17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B44" s="14">
         <v>480</v>
@@ -3009,21 +3054,21 @@
         <v>240</v>
       </c>
       <c r="K44" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L44" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M44" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N44" s="17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B45" s="14">
         <v>480</v>
@@ -3055,19 +3100,19 @@
         <v>260</v>
       </c>
       <c r="K45" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L45" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M45" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N45" s="17"/>
     </row>
     <row r="46" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A46" s="13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B46" s="14">
         <v>480</v>
@@ -3099,21 +3144,21 @@
         <v>150</v>
       </c>
       <c r="K46" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L46" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M46" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N46" s="17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="58" x14ac:dyDescent="0.35">
       <c r="A47" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B47" s="14">
         <v>480</v>
@@ -3148,18 +3193,18 @@
         <v>48</v>
       </c>
       <c r="L47" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M47" s="16" t="s">
         <v>49</v>
       </c>
       <c r="N47" s="17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B48" s="14">
         <v>480</v>
@@ -3191,21 +3236,21 @@
         <v>180</v>
       </c>
       <c r="K48" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L48" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M48" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N48" s="17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A49" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B49" s="14">
         <v>420</v>
@@ -3237,21 +3282,21 @@
         <v>50</v>
       </c>
       <c r="K49" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L49" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M49" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N49" s="17" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B50" s="14">
         <v>480</v>
@@ -3283,19 +3328,19 @@
         <v>180</v>
       </c>
       <c r="K50" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L50" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M50" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N50" s="17"/>
     </row>
     <row r="51" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A51" s="13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B51" s="14">
         <v>480</v>
@@ -3327,21 +3372,21 @@
         <v>220</v>
       </c>
       <c r="K51" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L51" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M51" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N51" s="17" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B52" s="14">
         <v>420</v>
@@ -3373,21 +3418,21 @@
         <v>420</v>
       </c>
       <c r="K52" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="L52" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="L52" s="16" t="s">
+      <c r="M52" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N52" s="17" t="s">
         <v>139</v>
-      </c>
-      <c r="M52" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="N52" s="17" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="53" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A53" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B53" s="14">
         <v>480</v>
@@ -3419,21 +3464,21 @@
         <v>250</v>
       </c>
       <c r="K53" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L53" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M53" s="16" t="s">
         <v>49</v>
       </c>
       <c r="N53" s="17" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A54" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B54" s="14">
         <v>480</v>
@@ -3465,21 +3510,21 @@
         <v>340</v>
       </c>
       <c r="K54" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L54" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M54" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N54" s="17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="55" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A55" s="13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B55" s="14">
         <v>480</v>
@@ -3511,16 +3556,16 @@
         <v>230</v>
       </c>
       <c r="K55" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L55" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M55" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N55" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.35">
@@ -3557,13 +3602,13 @@
         <v>250</v>
       </c>
       <c r="K56" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L56" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M56" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N56" s="17"/>
     </row>
@@ -3601,16 +3646,16 @@
         <v>200</v>
       </c>
       <c r="K57" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L57" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M57" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N57" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.35">
@@ -3647,16 +3692,16 @@
         <v>80</v>
       </c>
       <c r="K58" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L58" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M58" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N58" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="59" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
@@ -3693,16 +3738,16 @@
         <v>50</v>
       </c>
       <c r="K59" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L59" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M59" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N59" s="17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.35">
@@ -3739,13 +3784,13 @@
         <v>90</v>
       </c>
       <c r="K60" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L60" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M60" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N60" s="17"/>
     </row>
@@ -3783,16 +3828,16 @@
         <v>110</v>
       </c>
       <c r="K61" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L61" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M61" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N61" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.35">
@@ -3829,13 +3874,13 @@
         <v>100</v>
       </c>
       <c r="K62" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L62" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M62" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N62" s="17"/>
     </row>
@@ -3923,10 +3968,10 @@
         <v>58</v>
       </c>
       <c r="M64" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N64" s="17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="65" spans="1:14" ht="29" x14ac:dyDescent="0.35">
@@ -3966,13 +4011,13 @@
         <v>48</v>
       </c>
       <c r="L65" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M65" s="16" t="s">
         <v>49</v>
       </c>
       <c r="N65" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="66" spans="1:14" ht="29" x14ac:dyDescent="0.35">
@@ -4009,16 +4054,16 @@
         <v>220</v>
       </c>
       <c r="K66" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L66" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M66" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N66" s="17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="67" spans="1:14" ht="29" x14ac:dyDescent="0.35">
@@ -4055,237 +4100,459 @@
         <v>200</v>
       </c>
       <c r="K67" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L67" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M67" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N67" s="17" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A68" s="13"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="16"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="16"/>
-      <c r="N68" s="17"/>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A69" s="13"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
-      <c r="I69" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
-      <c r="N69" s="17"/>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A70" s="13"/>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
-        <v/>
-      </c>
-      <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
-        <v/>
-      </c>
-      <c r="K70" s="16"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="16"/>
-      <c r="N70" s="17"/>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A71" s="13"/>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
-      <c r="I71" s="15" t="str">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A68" s="21">
+        <v>46308</v>
+      </c>
+      <c r="B68" s="22">
+        <v>480</v>
+      </c>
+      <c r="C68" s="22">
+        <v>60</v>
+      </c>
+      <c r="D68" s="22">
+        <v>300</v>
+      </c>
+      <c r="E68" s="22">
+        <v>200</v>
+      </c>
+      <c r="F68" s="22">
+        <v>0</v>
+      </c>
+      <c r="G68" s="22">
+        <v>0</v>
+      </c>
+      <c r="H68" s="22">
+        <v>180</v>
+      </c>
+      <c r="I68" s="23">
+        <v>1220</v>
+      </c>
+      <c r="J68" s="23">
+        <v>220</v>
+      </c>
+      <c r="K68" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="L68" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="M68" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="N68" s="25" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A69" s="21">
+        <v>46309</v>
+      </c>
+      <c r="B69" s="22">
+        <v>480</v>
+      </c>
+      <c r="C69" s="22">
+        <v>70</v>
+      </c>
+      <c r="D69" s="22">
+        <v>250</v>
+      </c>
+      <c r="E69" s="22">
+        <v>220</v>
+      </c>
+      <c r="F69" s="22">
+        <v>0</v>
+      </c>
+      <c r="G69" s="22">
+        <v>0</v>
+      </c>
+      <c r="H69" s="22">
+        <v>200</v>
+      </c>
+      <c r="I69" s="23">
+        <v>1220</v>
+      </c>
+      <c r="J69" s="23">
+        <v>220</v>
+      </c>
+      <c r="K69" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="L69" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="M69" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="N69" s="25" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A70" s="21">
+        <v>46310</v>
+      </c>
+      <c r="B70" s="22">
+        <v>480</v>
+      </c>
+      <c r="C70" s="22">
+        <v>60</v>
+      </c>
+      <c r="D70" s="22">
+        <v>300</v>
+      </c>
+      <c r="E70" s="22">
+        <v>120</v>
+      </c>
+      <c r="F70" s="22">
+        <v>0</v>
+      </c>
+      <c r="G70" s="22">
+        <v>0</v>
+      </c>
+      <c r="H70" s="22">
+        <v>180</v>
+      </c>
+      <c r="I70" s="23">
+        <v>1140</v>
+      </c>
+      <c r="J70" s="23">
+        <v>300</v>
+      </c>
+      <c r="K70" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="L70" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="M70" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="N70" s="25" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A71" s="21">
+        <v>46311</v>
+      </c>
+      <c r="B71" s="22">
+        <v>480</v>
+      </c>
+      <c r="C71" s="22">
+        <v>70</v>
+      </c>
+      <c r="D71" s="22">
+        <v>250</v>
+      </c>
+      <c r="E71" s="22">
+        <v>240</v>
+      </c>
+      <c r="F71" s="22">
+        <v>0</v>
+      </c>
+      <c r="G71" s="22">
+        <v>0</v>
+      </c>
+      <c r="H71" s="22">
+        <v>200</v>
+      </c>
+      <c r="I71" s="23">
+        <v>1240</v>
+      </c>
+      <c r="J71" s="23">
+        <v>200</v>
+      </c>
+      <c r="K71" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="L71" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="M71" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="N71" s="25" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A72" s="21">
+        <v>46312</v>
+      </c>
+      <c r="B72" s="22">
+        <v>480</v>
+      </c>
+      <c r="C72" s="22">
+        <v>60</v>
+      </c>
+      <c r="D72" s="22">
+        <v>300</v>
+      </c>
+      <c r="E72" s="22">
+        <v>200</v>
+      </c>
+      <c r="F72" s="22">
+        <v>0</v>
+      </c>
+      <c r="G72" s="22">
+        <v>0</v>
+      </c>
+      <c r="H72" s="22">
+        <v>180</v>
+      </c>
+      <c r="I72" s="23">
+        <v>1220</v>
+      </c>
+      <c r="J72" s="23">
+        <v>220</v>
+      </c>
+      <c r="K72" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="L72" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="M72" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="N72" s="25" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A73" s="21">
+        <v>46313</v>
+      </c>
+      <c r="B73" s="22">
+        <v>480</v>
+      </c>
+      <c r="C73" s="22">
+        <v>60</v>
+      </c>
+      <c r="D73" s="22">
+        <v>250</v>
+      </c>
+      <c r="E73" s="22">
+        <v>180</v>
+      </c>
+      <c r="F73" s="22">
+        <v>0</v>
+      </c>
+      <c r="G73" s="22">
+        <v>0</v>
+      </c>
+      <c r="H73" s="22">
+        <v>200</v>
+      </c>
+      <c r="I73" s="23">
+        <v>1170</v>
+      </c>
+      <c r="J73" s="23">
+        <v>270</v>
+      </c>
+      <c r="K73" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="L73" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="M73" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="N73" s="25" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A74" s="21">
+        <v>46314</v>
+      </c>
+      <c r="B74" s="22">
+        <v>480</v>
+      </c>
+      <c r="C74" s="22">
+        <v>60</v>
+      </c>
+      <c r="D74" s="22">
+        <v>220</v>
+      </c>
+      <c r="E74" s="22">
+        <v>180</v>
+      </c>
+      <c r="F74" s="22">
+        <v>150</v>
+      </c>
+      <c r="G74" s="22">
+        <v>3</v>
+      </c>
+      <c r="H74" s="22">
+        <v>180</v>
+      </c>
+      <c r="I74" s="23">
+        <v>1270</v>
+      </c>
+      <c r="J74" s="23">
+        <v>170</v>
+      </c>
+      <c r="K74" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="L74" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="M74" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="N74" s="25" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A75" s="21">
+        <v>46315</v>
+      </c>
+      <c r="B75" s="22">
+        <v>480</v>
+      </c>
+      <c r="C75" s="22">
+        <v>60</v>
+      </c>
+      <c r="D75" s="22">
+        <v>360</v>
+      </c>
+      <c r="E75" s="22">
+        <v>180</v>
+      </c>
+      <c r="F75" s="22">
+        <v>0</v>
+      </c>
+      <c r="G75" s="22">
+        <v>0</v>
+      </c>
+      <c r="H75" s="22">
+        <v>200</v>
+      </c>
+      <c r="I75" s="23">
+        <v>1280</v>
+      </c>
+      <c r="J75" s="23">
+        <v>160</v>
+      </c>
+      <c r="K75" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="L75" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="M75" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="N75" s="25" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A76" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B76" s="14">
+        <v>480</v>
+      </c>
+      <c r="C76" s="14">
+        <v>60</v>
+      </c>
+      <c r="D76" s="14">
+        <v>300</v>
+      </c>
+      <c r="E76" s="14">
+        <v>180</v>
+      </c>
+      <c r="F76" s="14">
+        <v>200</v>
+      </c>
+      <c r="G76" s="14">
+        <v>4</v>
+      </c>
+      <c r="H76" s="14">
+        <v>180</v>
+      </c>
+      <c r="I76" s="15">
+        <f t="shared" ref="I70:I133" si="2">IF(SUM(B76:F76,H76)=0,"",SUM(B76:F76,H76))</f>
+        <v>1400</v>
+      </c>
+      <c r="J76" s="15">
+        <f t="shared" ref="J70:J133" si="3">IF(I76="","",1440-I76)</f>
+        <v>40</v>
+      </c>
+      <c r="K76" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="L76" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="M76" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="N76" s="25" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A77" s="13">
+        <v>46317</v>
+      </c>
+      <c r="B77" s="14">
+        <v>480</v>
+      </c>
+      <c r="C77" s="14">
+        <v>70</v>
+      </c>
+      <c r="D77" s="14">
+        <v>120</v>
+      </c>
+      <c r="E77" s="14">
+        <v>200</v>
+      </c>
+      <c r="F77" s="14">
+        <v>350</v>
+      </c>
+      <c r="G77" s="14">
+        <v>7</v>
+      </c>
+      <c r="H77" s="14">
+        <v>180</v>
+      </c>
+      <c r="I77" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="15" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J77" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K71" s="16"/>
-      <c r="L71" s="16"/>
-      <c r="M71" s="16"/>
-      <c r="N71" s="17"/>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A72" s="13"/>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
-      <c r="I72" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K72" s="16"/>
-      <c r="L72" s="16"/>
-      <c r="M72" s="16"/>
-      <c r="N72" s="17"/>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A73" s="13"/>
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K73" s="16"/>
-      <c r="L73" s="16"/>
-      <c r="M73" s="16"/>
-      <c r="N73" s="17"/>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A74" s="13"/>
-      <c r="B74" s="14"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
-      <c r="I74" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J74" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K74" s="16"/>
-      <c r="L74" s="16"/>
-      <c r="M74" s="16"/>
-      <c r="N74" s="17"/>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A75" s="13"/>
-      <c r="B75" s="14"/>
-      <c r="C75" s="14"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="14"/>
-      <c r="H75" s="14"/>
-      <c r="I75" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J75" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K75" s="16"/>
-      <c r="L75" s="16"/>
-      <c r="M75" s="16"/>
-      <c r="N75" s="17"/>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A76" s="13"/>
-      <c r="B76" s="14"/>
-      <c r="C76" s="14"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
-      <c r="G76" s="14"/>
-      <c r="H76" s="14"/>
-      <c r="I76" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J76" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K76" s="16"/>
-      <c r="L76" s="16"/>
-      <c r="M76" s="16"/>
-      <c r="N76" s="17"/>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A77" s="13"/>
-      <c r="B77" s="14"/>
-      <c r="C77" s="14"/>
-      <c r="D77" s="14"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="14"/>
-      <c r="G77" s="14"/>
-      <c r="H77" s="14"/>
-      <c r="I77" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J77" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K77" s="16"/>
-      <c r="L77" s="16"/>
-      <c r="M77" s="16"/>
-      <c r="N77" s="17"/>
+        <v>40</v>
+      </c>
+      <c r="K77" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="L77" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="M77" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="N77" s="25"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A78" s="13"/>
@@ -4304,10 +4571,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K78" s="16"/>
-      <c r="L78" s="16"/>
-      <c r="M78" s="16"/>
-      <c r="N78" s="17"/>
+      <c r="K78" s="24"/>
+      <c r="L78" s="24"/>
+      <c r="M78" s="24"/>
+      <c r="N78" s="25"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A79" s="13"/>
@@ -4326,10 +4593,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K79" s="16"/>
-      <c r="L79" s="16"/>
-      <c r="M79" s="16"/>
-      <c r="N79" s="17"/>
+      <c r="K79" s="24"/>
+      <c r="L79" s="24"/>
+      <c r="M79" s="24"/>
+      <c r="N79" s="25"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A80" s="13"/>
@@ -4348,10 +4615,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K80" s="16"/>
-      <c r="L80" s="16"/>
-      <c r="M80" s="16"/>
-      <c r="N80" s="17"/>
+      <c r="K80" s="24"/>
+      <c r="L80" s="24"/>
+      <c r="M80" s="24"/>
+      <c r="N80" s="25"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A81" s="13"/>
@@ -4370,10 +4637,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K81" s="16"/>
-      <c r="L81" s="16"/>
-      <c r="M81" s="16"/>
-      <c r="N81" s="17"/>
+      <c r="K81" s="24"/>
+      <c r="L81" s="24"/>
+      <c r="M81" s="24"/>
+      <c r="N81" s="25"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A82" s="13"/>
@@ -4392,10 +4659,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K82" s="16"/>
-      <c r="L82" s="16"/>
-      <c r="M82" s="16"/>
-      <c r="N82" s="17"/>
+      <c r="K82" s="24"/>
+      <c r="L82" s="24"/>
+      <c r="M82" s="24"/>
+      <c r="N82" s="25"/>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A83" s="13"/>
@@ -4414,10 +4681,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K83" s="16"/>
-      <c r="L83" s="16"/>
-      <c r="M83" s="16"/>
-      <c r="N83" s="17"/>
+      <c r="K83" s="24"/>
+      <c r="L83" s="24"/>
+      <c r="M83" s="24"/>
+      <c r="N83" s="25"/>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A84" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87ECC43E-8056-49C3-87AA-F2A889798450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADDF9FCF-899E-44B7-9BD2-358D8489B028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="164">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -706,9 +706,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -724,6 +721,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1207,74 +1207,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="25">
         <v>12604409</v>
       </c>
-      <c r="G2" s="20"/>
+      <c r="G2" s="25"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="G3" s="20"/>
+      <c r="G3" s="25"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
     </row>
     <row r="5" spans="1:14" ht="42" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
@@ -1362,11 +1362,11 @@
         <v>120</v>
       </c>
       <c r="I7" s="15">
-        <f t="shared" ref="I7:I69" si="0">IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
+        <f t="shared" ref="I7:I67" si="0">IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
         <v>1240</v>
       </c>
       <c r="J7" s="15">
-        <f t="shared" ref="J7:J69" si="1">IF(I7="","",1440-I7)</f>
+        <f t="shared" ref="J7:J67" si="1">IF(I7="","",1440-I7)</f>
         <v>200</v>
       </c>
       <c r="K7" s="16" t="s">
@@ -4113,354 +4113,354 @@
       </c>
     </row>
     <row r="68" spans="1:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="A68" s="21">
+      <c r="A68" s="18">
         <v>46308</v>
       </c>
-      <c r="B68" s="22">
+      <c r="B68" s="19">
         <v>480</v>
       </c>
-      <c r="C68" s="22">
+      <c r="C68" s="19">
         <v>60</v>
       </c>
-      <c r="D68" s="22">
+      <c r="D68" s="19">
         <v>300</v>
       </c>
-      <c r="E68" s="22">
+      <c r="E68" s="19">
         <v>200</v>
       </c>
-      <c r="F68" s="22">
+      <c r="F68" s="19">
         <v>0</v>
       </c>
-      <c r="G68" s="22">
+      <c r="G68" s="19">
         <v>0</v>
       </c>
-      <c r="H68" s="22">
+      <c r="H68" s="19">
         <v>180</v>
       </c>
-      <c r="I68" s="23">
+      <c r="I68" s="20">
         <v>1220</v>
       </c>
-      <c r="J68" s="23">
+      <c r="J68" s="20">
         <v>220</v>
       </c>
-      <c r="K68" s="24" t="s">
+      <c r="K68" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="L68" s="24" t="s">
+      <c r="L68" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="M68" s="24" t="s">
+      <c r="M68" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="N68" s="25" t="s">
+      <c r="N68" s="22" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="69" spans="1:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="A69" s="21">
+      <c r="A69" s="18">
         <v>46309</v>
       </c>
-      <c r="B69" s="22">
+      <c r="B69" s="19">
         <v>480</v>
       </c>
-      <c r="C69" s="22">
+      <c r="C69" s="19">
         <v>70</v>
       </c>
-      <c r="D69" s="22">
+      <c r="D69" s="19">
         <v>250</v>
       </c>
-      <c r="E69" s="22">
+      <c r="E69" s="19">
         <v>220</v>
       </c>
-      <c r="F69" s="22">
+      <c r="F69" s="19">
         <v>0</v>
       </c>
-      <c r="G69" s="22">
+      <c r="G69" s="19">
         <v>0</v>
       </c>
-      <c r="H69" s="22">
+      <c r="H69" s="19">
         <v>200</v>
       </c>
-      <c r="I69" s="23">
+      <c r="I69" s="20">
         <v>1220</v>
       </c>
-      <c r="J69" s="23">
+      <c r="J69" s="20">
         <v>220</v>
       </c>
-      <c r="K69" s="24" t="s">
+      <c r="K69" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="L69" s="24" t="s">
+      <c r="L69" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="M69" s="24" t="s">
+      <c r="M69" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="N69" s="25" t="s">
+      <c r="N69" s="22" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="70" spans="1:14" ht="58" x14ac:dyDescent="0.35">
-      <c r="A70" s="21">
+      <c r="A70" s="18">
         <v>46310</v>
       </c>
-      <c r="B70" s="22">
+      <c r="B70" s="19">
         <v>480</v>
       </c>
-      <c r="C70" s="22">
+      <c r="C70" s="19">
         <v>60</v>
       </c>
-      <c r="D70" s="22">
+      <c r="D70" s="19">
         <v>300</v>
       </c>
-      <c r="E70" s="22">
+      <c r="E70" s="19">
         <v>120</v>
       </c>
-      <c r="F70" s="22">
+      <c r="F70" s="19">
         <v>0</v>
       </c>
-      <c r="G70" s="22">
+      <c r="G70" s="19">
         <v>0</v>
       </c>
-      <c r="H70" s="22">
+      <c r="H70" s="19">
         <v>180</v>
       </c>
-      <c r="I70" s="23">
+      <c r="I70" s="20">
         <v>1140</v>
       </c>
-      <c r="J70" s="23">
+      <c r="J70" s="20">
         <v>300</v>
       </c>
-      <c r="K70" s="24" t="s">
+      <c r="K70" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="L70" s="24" t="s">
+      <c r="L70" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="M70" s="24" t="s">
+      <c r="M70" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="N70" s="25" t="s">
+      <c r="N70" s="22" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="71" spans="1:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="A71" s="21">
+      <c r="A71" s="18">
         <v>46311</v>
       </c>
-      <c r="B71" s="22">
+      <c r="B71" s="19">
         <v>480</v>
       </c>
-      <c r="C71" s="22">
+      <c r="C71" s="19">
         <v>70</v>
       </c>
-      <c r="D71" s="22">
+      <c r="D71" s="19">
         <v>250</v>
       </c>
-      <c r="E71" s="22">
+      <c r="E71" s="19">
         <v>240</v>
       </c>
-      <c r="F71" s="22">
+      <c r="F71" s="19">
         <v>0</v>
       </c>
-      <c r="G71" s="22">
+      <c r="G71" s="19">
         <v>0</v>
       </c>
-      <c r="H71" s="22">
+      <c r="H71" s="19">
         <v>200</v>
       </c>
-      <c r="I71" s="23">
+      <c r="I71" s="20">
         <v>1240</v>
       </c>
-      <c r="J71" s="23">
+      <c r="J71" s="20">
         <v>200</v>
       </c>
-      <c r="K71" s="24" t="s">
+      <c r="K71" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="L71" s="24" t="s">
+      <c r="L71" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="M71" s="24" t="s">
+      <c r="M71" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="N71" s="25" t="s">
+      <c r="N71" s="22" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A72" s="21">
+      <c r="A72" s="18">
         <v>46312</v>
       </c>
-      <c r="B72" s="22">
+      <c r="B72" s="19">
         <v>480</v>
       </c>
-      <c r="C72" s="22">
+      <c r="C72" s="19">
         <v>60</v>
       </c>
-      <c r="D72" s="22">
+      <c r="D72" s="19">
         <v>300</v>
       </c>
-      <c r="E72" s="22">
+      <c r="E72" s="19">
         <v>200</v>
       </c>
-      <c r="F72" s="22">
+      <c r="F72" s="19">
         <v>0</v>
       </c>
-      <c r="G72" s="22">
+      <c r="G72" s="19">
         <v>0</v>
       </c>
-      <c r="H72" s="22">
+      <c r="H72" s="19">
         <v>180</v>
       </c>
-      <c r="I72" s="23">
+      <c r="I72" s="20">
         <v>1220</v>
       </c>
-      <c r="J72" s="23">
+      <c r="J72" s="20">
         <v>220</v>
       </c>
-      <c r="K72" s="24" t="s">
+      <c r="K72" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="L72" s="24" t="s">
+      <c r="L72" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="M72" s="24" t="s">
+      <c r="M72" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="N72" s="25" t="s">
+      <c r="N72" s="22" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A73" s="21">
+      <c r="A73" s="18">
         <v>46313</v>
       </c>
-      <c r="B73" s="22">
+      <c r="B73" s="19">
         <v>480</v>
       </c>
-      <c r="C73" s="22">
+      <c r="C73" s="19">
         <v>60</v>
       </c>
-      <c r="D73" s="22">
+      <c r="D73" s="19">
         <v>250</v>
       </c>
-      <c r="E73" s="22">
+      <c r="E73" s="19">
         <v>180</v>
       </c>
-      <c r="F73" s="22">
+      <c r="F73" s="19">
         <v>0</v>
       </c>
-      <c r="G73" s="22">
+      <c r="G73" s="19">
         <v>0</v>
       </c>
-      <c r="H73" s="22">
+      <c r="H73" s="19">
         <v>200</v>
       </c>
-      <c r="I73" s="23">
+      <c r="I73" s="20">
         <v>1170</v>
       </c>
-      <c r="J73" s="23">
+      <c r="J73" s="20">
         <v>270</v>
       </c>
-      <c r="K73" s="24" t="s">
+      <c r="K73" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="L73" s="24" t="s">
+      <c r="L73" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="M73" s="24" t="s">
+      <c r="M73" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="N73" s="25" t="s">
+      <c r="N73" s="22" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="74" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A74" s="21">
+      <c r="A74" s="18">
         <v>46314</v>
       </c>
-      <c r="B74" s="22">
+      <c r="B74" s="19">
         <v>480</v>
       </c>
-      <c r="C74" s="22">
+      <c r="C74" s="19">
         <v>60</v>
       </c>
-      <c r="D74" s="22">
+      <c r="D74" s="19">
         <v>220</v>
       </c>
-      <c r="E74" s="22">
+      <c r="E74" s="19">
         <v>180</v>
       </c>
-      <c r="F74" s="22">
+      <c r="F74" s="19">
         <v>150</v>
       </c>
-      <c r="G74" s="22">
+      <c r="G74" s="19">
         <v>3</v>
       </c>
-      <c r="H74" s="22">
+      <c r="H74" s="19">
         <v>180</v>
       </c>
-      <c r="I74" s="23">
+      <c r="I74" s="20">
         <v>1270</v>
       </c>
-      <c r="J74" s="23">
+      <c r="J74" s="20">
         <v>170</v>
       </c>
-      <c r="K74" s="24" t="s">
+      <c r="K74" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="L74" s="24" t="s">
+      <c r="L74" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="M74" s="24" t="s">
+      <c r="M74" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="N74" s="25" t="s">
+      <c r="N74" s="22" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="75" spans="1:14" ht="58" x14ac:dyDescent="0.35">
-      <c r="A75" s="21">
+      <c r="A75" s="18">
         <v>46315</v>
       </c>
-      <c r="B75" s="22">
+      <c r="B75" s="19">
         <v>480</v>
       </c>
-      <c r="C75" s="22">
+      <c r="C75" s="19">
         <v>60</v>
       </c>
-      <c r="D75" s="22">
+      <c r="D75" s="19">
         <v>360</v>
       </c>
-      <c r="E75" s="22">
+      <c r="E75" s="19">
         <v>180</v>
       </c>
-      <c r="F75" s="22">
+      <c r="F75" s="19">
         <v>0</v>
       </c>
-      <c r="G75" s="22">
+      <c r="G75" s="19">
         <v>0</v>
       </c>
-      <c r="H75" s="22">
+      <c r="H75" s="19">
         <v>200</v>
       </c>
-      <c r="I75" s="23">
+      <c r="I75" s="20">
         <v>1280</v>
       </c>
-      <c r="J75" s="23">
+      <c r="J75" s="20">
         <v>160</v>
       </c>
-      <c r="K75" s="24" t="s">
+      <c r="K75" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="L75" s="24" t="s">
+      <c r="L75" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="M75" s="24" t="s">
+      <c r="M75" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="N75" s="25" t="s">
+      <c r="N75" s="22" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4490,23 +4490,23 @@
         <v>180</v>
       </c>
       <c r="I76" s="15">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B76:F76,H76)=0,"",SUM(B76:F76,H76))</f>
+        <f t="shared" ref="I76:I133" si="2">IF(SUM(B76:F76,H76)=0,"",SUM(B76:F76,H76))</f>
         <v>1400</v>
       </c>
       <c r="J76" s="15">
-        <f t="shared" ref="J70:J133" si="3">IF(I76="","",1440-I76)</f>
+        <f t="shared" ref="J76:J133" si="3">IF(I76="","",1440-I76)</f>
         <v>40</v>
       </c>
-      <c r="K76" s="24" t="s">
+      <c r="K76" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="L76" s="24" t="s">
+      <c r="L76" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="M76" s="24" t="s">
+      <c r="M76" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="N76" s="25" t="s">
+      <c r="N76" s="22" t="s">
         <v>163</v>
       </c>
     </row>
@@ -4543,38 +4543,60 @@
         <f t="shared" si="3"/>
         <v>40</v>
       </c>
-      <c r="K77" s="24" t="s">
+      <c r="K77" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="L77" s="24" t="s">
+      <c r="L77" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="M77" s="24" t="s">
+      <c r="M77" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="N77" s="25"/>
+      <c r="N77" s="22"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A78" s="13"/>
-      <c r="B78" s="14"/>
-      <c r="C78" s="14"/>
-      <c r="D78" s="14"/>
-      <c r="E78" s="14"/>
-      <c r="F78" s="14"/>
-      <c r="G78" s="14"/>
-      <c r="H78" s="14"/>
-      <c r="I78" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J78" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K78" s="24"/>
-      <c r="L78" s="24"/>
-      <c r="M78" s="24"/>
-      <c r="N78" s="25"/>
+      <c r="A78" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B78" s="19">
+        <v>480</v>
+      </c>
+      <c r="C78" s="19">
+        <v>70</v>
+      </c>
+      <c r="D78" s="19">
+        <v>120</v>
+      </c>
+      <c r="E78" s="19">
+        <v>200</v>
+      </c>
+      <c r="F78" s="19">
+        <v>350</v>
+      </c>
+      <c r="G78" s="19">
+        <v>7</v>
+      </c>
+      <c r="H78" s="19">
+        <v>180</v>
+      </c>
+      <c r="I78" s="20">
+        <f t="shared" ref="I78" si="4">IF(SUM(B78:F78,H78)=0,"",SUM(B78:F78,H78))</f>
+        <v>1400</v>
+      </c>
+      <c r="J78" s="20">
+        <f t="shared" ref="J78" si="5">IF(I78="","",1440-I78)</f>
+        <v>40</v>
+      </c>
+      <c r="K78" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="L78" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="M78" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="N78" s="22"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A79" s="13"/>
@@ -4593,10 +4615,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K79" s="24"/>
-      <c r="L79" s="24"/>
-      <c r="M79" s="24"/>
-      <c r="N79" s="25"/>
+      <c r="K79" s="21"/>
+      <c r="L79" s="21"/>
+      <c r="M79" s="21"/>
+      <c r="N79" s="22"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A80" s="13"/>
@@ -4615,10 +4637,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K80" s="24"/>
-      <c r="L80" s="24"/>
-      <c r="M80" s="24"/>
-      <c r="N80" s="25"/>
+      <c r="K80" s="21"/>
+      <c r="L80" s="21"/>
+      <c r="M80" s="21"/>
+      <c r="N80" s="22"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A81" s="13"/>
@@ -4637,10 +4659,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K81" s="24"/>
-      <c r="L81" s="24"/>
-      <c r="M81" s="24"/>
-      <c r="N81" s="25"/>
+      <c r="K81" s="21"/>
+      <c r="L81" s="21"/>
+      <c r="M81" s="21"/>
+      <c r="N81" s="22"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A82" s="13"/>
@@ -4659,10 +4681,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K82" s="24"/>
-      <c r="L82" s="24"/>
-      <c r="M82" s="24"/>
-      <c r="N82" s="25"/>
+      <c r="K82" s="21"/>
+      <c r="L82" s="21"/>
+      <c r="M82" s="21"/>
+      <c r="N82" s="22"/>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A83" s="13"/>
@@ -4681,10 +4703,10 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K83" s="24"/>
-      <c r="L83" s="24"/>
-      <c r="M83" s="24"/>
-      <c r="N83" s="25"/>
+      <c r="K83" s="21"/>
+      <c r="L83" s="21"/>
+      <c r="M83" s="21"/>
+      <c r="N83" s="22"/>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A84" s="13"/>
@@ -5796,11 +5818,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="6">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="7">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -5818,11 +5840,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -5840,11 +5862,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -5862,11 +5884,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -5884,11 +5906,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -5906,11 +5928,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -5928,11 +5950,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -5950,11 +5972,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -5972,11 +5994,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -5994,11 +6016,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -6016,11 +6038,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -6038,11 +6060,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -6060,11 +6082,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -6082,11 +6104,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -6104,11 +6126,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -6126,11 +6148,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -6148,11 +6170,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -6170,11 +6192,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -6192,11 +6214,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -6214,11 +6236,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -6236,11 +6258,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -6258,11 +6280,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -6280,11 +6302,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -6302,11 +6324,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -6324,11 +6346,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -6346,11 +6368,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -6368,11 +6390,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -6390,11 +6412,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -6412,11 +6434,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -6434,11 +6456,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -6456,11 +6478,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -6478,11 +6500,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -6500,11 +6522,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -6522,11 +6544,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -6544,11 +6566,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -6566,11 +6588,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -6588,11 +6610,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -6610,11 +6632,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -6632,11 +6654,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -6654,11 +6676,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -6676,11 +6698,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -6698,11 +6720,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -6720,11 +6742,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -6742,11 +6764,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -6764,11 +6786,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -6786,11 +6808,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -6808,11 +6830,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -6830,11 +6852,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -6852,11 +6874,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -6874,11 +6896,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -6896,11 +6918,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -6918,11 +6940,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -6940,11 +6962,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -6962,11 +6984,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -6984,11 +7006,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -7006,11 +7028,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -7028,11 +7050,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -7050,11 +7072,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -7072,11 +7094,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -7094,11 +7116,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -7116,11 +7138,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -7138,11 +7160,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -7160,11 +7182,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -7182,11 +7204,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -7204,11 +7226,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="8">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="9">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -7226,11 +7248,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -7248,11 +7270,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -7270,11 +7292,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -7292,11 +7314,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -7314,11 +7336,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -7336,11 +7358,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -7358,11 +7380,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -7380,11 +7402,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -7402,11 +7424,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -7424,11 +7446,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -7446,11 +7468,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -7468,11 +7490,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -7490,11 +7512,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -7512,11 +7534,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -7534,11 +7556,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -7556,11 +7578,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -7578,11 +7600,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -7600,11 +7622,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -7622,11 +7644,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -7644,11 +7666,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -7666,11 +7688,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -7688,11 +7710,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -7710,11 +7732,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -7732,11 +7754,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -7754,11 +7776,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -7776,11 +7798,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -7798,11 +7820,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -7820,11 +7842,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -7842,11 +7864,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -7864,11 +7886,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -7886,11 +7908,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -7908,11 +7930,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -7930,11 +7952,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -7952,11 +7974,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -7974,11 +7996,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -7996,11 +8018,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -8018,11 +8040,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -8040,11 +8062,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -8062,11 +8084,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -8084,11 +8106,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -8106,11 +8128,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -8128,11 +8150,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -8150,11 +8172,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -8172,11 +8194,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -8194,11 +8216,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -8216,11 +8238,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -8238,11 +8260,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -8260,11 +8282,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -8282,11 +8304,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -8304,11 +8326,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -8326,11 +8348,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -8348,11 +8370,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -8370,11 +8392,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -8392,11 +8414,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -8414,11 +8436,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -8436,11 +8458,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -8458,11 +8480,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -8480,11 +8502,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -8502,11 +8524,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -8524,11 +8546,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -8546,11 +8568,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -8568,11 +8590,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -8590,11 +8612,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -8612,11 +8634,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="10">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="11">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -8634,11 +8656,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -8656,11 +8678,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -8678,11 +8700,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -8700,11 +8722,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -8722,11 +8744,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -8744,11 +8766,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -8766,11 +8788,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -8788,11 +8810,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -8810,11 +8832,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -8832,11 +8854,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -8854,11 +8876,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -8876,11 +8898,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -8898,11 +8920,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -8920,11 +8942,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -8942,11 +8964,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -8964,11 +8986,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -8986,11 +9008,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -9008,11 +9030,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -9030,11 +9052,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -9052,11 +9074,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -9074,11 +9096,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -9096,11 +9118,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -9118,11 +9140,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -9140,11 +9162,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -9162,11 +9184,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -9184,11 +9206,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -9206,11 +9228,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -9228,11 +9250,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -9250,11 +9272,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -9272,11 +9294,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -9294,11 +9316,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -9316,11 +9338,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -9338,11 +9360,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -9360,11 +9382,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -9382,11 +9404,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -9404,11 +9426,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -9426,11 +9448,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -9448,11 +9470,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -9470,11 +9492,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -9492,11 +9514,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -9514,11 +9536,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -9536,11 +9558,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -9558,11 +9580,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -9580,11 +9602,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -9602,11 +9624,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -9624,11 +9646,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -9646,11 +9668,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -9668,11 +9690,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -9690,11 +9712,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -9712,11 +9734,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -9734,11 +9756,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -9756,11 +9778,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -9778,11 +9800,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -9800,11 +9822,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -9822,11 +9844,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -9844,11 +9866,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -9866,11 +9888,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -9888,11 +9910,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -9910,11 +9932,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -9932,11 +9954,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -9954,11 +9976,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -9976,11 +9998,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -9998,11 +10020,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -10020,11 +10042,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="12">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="13">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -10042,11 +10064,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -10064,11 +10086,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -10086,11 +10108,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -10108,11 +10130,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -10130,11 +10152,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -10152,11 +10174,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -10174,11 +10196,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -10196,11 +10218,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -10218,11 +10240,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -10240,11 +10262,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -10262,11 +10284,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -10284,11 +10306,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -10306,11 +10328,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -10328,11 +10350,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -10350,11 +10372,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -10372,11 +10394,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -10394,11 +10416,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -10416,11 +10438,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -10438,11 +10460,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -10460,11 +10482,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -10482,11 +10504,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -10504,11 +10526,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -10526,11 +10548,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -10548,11 +10570,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -10570,11 +10592,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -10592,11 +10614,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -10614,11 +10636,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -10636,11 +10658,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -10658,11 +10680,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -10680,11 +10702,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -10702,11 +10724,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -10724,11 +10746,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -10746,11 +10768,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -10768,11 +10790,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -10790,11 +10812,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -10812,11 +10834,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -10834,11 +10856,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -10856,11 +10878,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -10878,11 +10900,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -10900,11 +10922,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -10922,11 +10944,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -10944,11 +10966,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -10966,11 +10988,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -10988,11 +11010,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -11010,11 +11032,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -11032,11 +11054,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -11054,11 +11076,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -11076,11 +11098,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -11098,11 +11120,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -11120,11 +11142,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -11142,11 +11164,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -11164,11 +11186,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -11186,11 +11208,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -11208,11 +11230,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -11230,11 +11252,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -11252,11 +11274,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -11274,11 +11296,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -11296,11 +11318,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -11318,11 +11340,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -11340,11 +11362,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -11362,11 +11384,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -11384,11 +11406,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -11406,11 +11428,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -11428,11 +11450,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="14">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="15">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -11450,11 +11472,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -11472,11 +11494,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -11494,11 +11516,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -11516,11 +11538,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -11538,11 +11560,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -11560,11 +11582,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -11582,11 +11604,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -11604,11 +11626,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -11626,11 +11648,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -11648,11 +11670,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -11670,11 +11692,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K401" s="16"/>
@@ -11705,7 +11727,7 @@
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401 N38" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="N38 M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADDF9FCF-899E-44B7-9BD2-358D8489B028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{633B7741-8467-459B-B32D-6ADF2454690E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="166">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -527,6 +527,12 @@
   </si>
   <si>
     <t>Today sir gave us CA of C++ and its also like python project.</t>
+  </si>
+  <si>
+    <t>Today feels like weather starts changing and finally I can say winter comes.</t>
+  </si>
+  <si>
+    <t>Nothing special, but winter is coming.</t>
   </si>
 </sst>
 </file>
@@ -4554,7 +4560,7 @@
       </c>
       <c r="N77" s="22"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A78" s="13">
         <v>46318</v>
       </c>
@@ -4562,33 +4568,33 @@
         <v>480</v>
       </c>
       <c r="C78" s="19">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D78" s="19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E78" s="19">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="F78" s="19">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G78" s="19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H78" s="19">
         <v>180</v>
       </c>
       <c r="I78" s="20">
         <f t="shared" ref="I78" si="4">IF(SUM(B78:F78,H78)=0,"",SUM(B78:F78,H78))</f>
-        <v>1400</v>
+        <v>1340</v>
       </c>
       <c r="J78" s="20">
         <f t="shared" ref="J78" si="5">IF(I78="","",1440-I78)</f>
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="K78" s="21" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="L78" s="21" t="s">
         <v>73</v>
@@ -4596,29 +4602,55 @@
       <c r="M78" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="N78" s="22"/>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A79" s="13"/>
-      <c r="B79" s="14"/>
-      <c r="C79" s="14"/>
-      <c r="D79" s="14"/>
-      <c r="E79" s="14"/>
-      <c r="F79" s="14"/>
-      <c r="G79" s="14"/>
-      <c r="H79" s="14"/>
-      <c r="I79" s="15" t="str">
+      <c r="N78" s="22" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A79" s="13">
+        <v>46319</v>
+      </c>
+      <c r="B79" s="14">
+        <v>480</v>
+      </c>
+      <c r="C79" s="14">
+        <v>60</v>
+      </c>
+      <c r="D79" s="14">
+        <v>300</v>
+      </c>
+      <c r="E79" s="14">
+        <v>240</v>
+      </c>
+      <c r="F79" s="14">
+        <v>0</v>
+      </c>
+      <c r="G79" s="14">
+        <v>0</v>
+      </c>
+      <c r="H79" s="14">
+        <v>180</v>
+      </c>
+      <c r="I79" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J79" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J79" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K79" s="21"/>
-      <c r="L79" s="21"/>
-      <c r="M79" s="21"/>
-      <c r="N79" s="22"/>
+        <v>180</v>
+      </c>
+      <c r="K79" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="L79" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="M79" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="N79" s="22" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A80" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{633B7741-8467-459B-B32D-6ADF2454690E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519F0769-04B3-4590-A3B6-D1B2CD11ABA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="167">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -533,6 +533,9 @@
   </si>
   <si>
     <t>Nothing special, but winter is coming.</t>
+  </si>
+  <si>
+    <t>Preparing for CA as well as for trip.</t>
   </si>
 </sst>
 </file>
@@ -4652,27 +4655,51 @@
         <v>164</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A80" s="13"/>
-      <c r="B80" s="14"/>
-      <c r="C80" s="14"/>
-      <c r="D80" s="14"/>
-      <c r="E80" s="14"/>
-      <c r="F80" s="14"/>
-      <c r="G80" s="14"/>
-      <c r="H80" s="14"/>
-      <c r="I80" s="15" t="str">
+    <row r="80" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A80" s="13">
+        <v>46320</v>
+      </c>
+      <c r="B80" s="14">
+        <v>480</v>
+      </c>
+      <c r="C80" s="14">
+        <v>60</v>
+      </c>
+      <c r="D80" s="14">
+        <v>240</v>
+      </c>
+      <c r="E80" s="14">
+        <v>180</v>
+      </c>
+      <c r="F80" s="14">
+        <v>0</v>
+      </c>
+      <c r="G80" s="14">
+        <v>0</v>
+      </c>
+      <c r="H80" s="14">
+        <v>240</v>
+      </c>
+      <c r="I80" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J80" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J80" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K80" s="21"/>
-      <c r="L80" s="21"/>
-      <c r="M80" s="21"/>
-      <c r="N80" s="22"/>
+        <v>240</v>
+      </c>
+      <c r="K80" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="L80" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="M80" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="N80" s="22" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A81" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519F0769-04B3-4590-A3B6-D1B2CD11ABA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F891AC78-2DBD-4704-9EE4-421991E428A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="168">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -536,6 +536,9 @@
   </si>
   <si>
     <t>Preparing for CA as well as for trip.</t>
+  </si>
+  <si>
+    <t>Participating in bhangra in SPECTRA</t>
   </si>
 </sst>
 </file>
@@ -4702,48 +4705,94 @@
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A81" s="13"/>
-      <c r="B81" s="14"/>
-      <c r="C81" s="14"/>
-      <c r="D81" s="14"/>
-      <c r="E81" s="14"/>
-      <c r="F81" s="14"/>
-      <c r="G81" s="14"/>
-      <c r="H81" s="14"/>
-      <c r="I81" s="15" t="str">
+      <c r="A81" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B81" s="14">
+        <v>480</v>
+      </c>
+      <c r="C81" s="14">
+        <v>60</v>
+      </c>
+      <c r="D81" s="14">
+        <v>350</v>
+      </c>
+      <c r="E81" s="14">
+        <v>180</v>
+      </c>
+      <c r="F81" s="14">
+        <v>0</v>
+      </c>
+      <c r="G81" s="14">
+        <v>0</v>
+      </c>
+      <c r="H81" s="14">
+        <v>180</v>
+      </c>
+      <c r="I81" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J81" s="15" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J81" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K81" s="21"/>
-      <c r="L81" s="21"/>
-      <c r="M81" s="21"/>
+        <v>190</v>
+      </c>
+      <c r="K81" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="L81" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="M81" s="21" t="s">
+        <v>77</v>
+      </c>
       <c r="N81" s="22"/>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A82" s="13"/>
-      <c r="B82" s="14"/>
-      <c r="C82" s="14"/>
-      <c r="D82" s="14"/>
-      <c r="E82" s="14"/>
-      <c r="F82" s="14"/>
-      <c r="G82" s="14"/>
-      <c r="H82" s="14"/>
-      <c r="I82" s="15" t="str">
+    <row r="82" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A82" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B82" s="14">
+        <v>420</v>
+      </c>
+      <c r="C82" s="14">
+        <v>60</v>
+      </c>
+      <c r="D82" s="14">
+        <v>180</v>
+      </c>
+      <c r="E82" s="14">
+        <v>220</v>
+      </c>
+      <c r="F82" s="14">
+        <v>250</v>
+      </c>
+      <c r="G82" s="14">
+        <v>5</v>
+      </c>
+      <c r="H82" s="14">
+        <v>200</v>
+      </c>
+      <c r="I82" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J82" s="15" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J82" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K82" s="21"/>
-      <c r="L82" s="21"/>
-      <c r="M82" s="21"/>
-      <c r="N82" s="22"/>
+        <v>110</v>
+      </c>
+      <c r="K82" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="L82" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="M82" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="N82" s="22" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A83" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F891AC78-2DBD-4704-9EE4-421991E428A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5ACBD20-D3F5-4D83-A3C1-68C5917A44B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="169">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -539,6 +539,9 @@
   </si>
   <si>
     <t>Participating in bhangra in SPECTRA</t>
+  </si>
+  <si>
+    <t>again suffering from fewer.</t>
   </si>
 </sst>
 </file>
@@ -4795,26 +4798,50 @@
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A83" s="13"/>
-      <c r="B83" s="14"/>
-      <c r="C83" s="14"/>
-      <c r="D83" s="14"/>
-      <c r="E83" s="14"/>
-      <c r="F83" s="14"/>
-      <c r="G83" s="14"/>
-      <c r="H83" s="14"/>
-      <c r="I83" s="15" t="str">
+      <c r="A83" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B83" s="14">
+        <v>480</v>
+      </c>
+      <c r="C83" s="14">
+        <v>60</v>
+      </c>
+      <c r="D83" s="14">
+        <v>200</v>
+      </c>
+      <c r="E83" s="14">
+        <v>180</v>
+      </c>
+      <c r="F83" s="14">
+        <v>150</v>
+      </c>
+      <c r="G83" s="14">
+        <v>3</v>
+      </c>
+      <c r="H83" s="14">
+        <v>180</v>
+      </c>
+      <c r="I83" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J83" s="15" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J83" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K83" s="21"/>
-      <c r="L83" s="21"/>
-      <c r="M83" s="21"/>
-      <c r="N83" s="22"/>
+        <v>190</v>
+      </c>
+      <c r="K83" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="L83" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="M83" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="N83" s="22" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A84" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5ACBD20-D3F5-4D83-A3C1-68C5917A44B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68DE94AA-1379-41DB-90E8-71B1C561DFEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="170">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -542,6 +542,9 @@
   </si>
   <si>
     <t>again suffering from fewer.</t>
+  </si>
+  <si>
+    <t>Practicing bhangra for SPECTRA.</t>
   </si>
 </sst>
 </file>
@@ -4844,26 +4847,50 @@
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A84" s="13"/>
-      <c r="B84" s="14"/>
-      <c r="C84" s="14"/>
-      <c r="D84" s="14"/>
-      <c r="E84" s="14"/>
-      <c r="F84" s="14"/>
-      <c r="G84" s="14"/>
-      <c r="H84" s="14"/>
-      <c r="I84" s="15" t="str">
+      <c r="A84" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B84" s="14">
+        <v>480</v>
+      </c>
+      <c r="C84" s="14">
+        <v>60</v>
+      </c>
+      <c r="D84" s="14">
+        <v>180</v>
+      </c>
+      <c r="E84" s="14">
+        <v>120</v>
+      </c>
+      <c r="F84" s="14">
+        <v>0</v>
+      </c>
+      <c r="G84" s="14">
+        <v>0</v>
+      </c>
+      <c r="H84" s="14">
+        <v>220</v>
+      </c>
+      <c r="I84" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J84" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J84" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K84" s="16"/>
-      <c r="L84" s="16"/>
-      <c r="M84" s="16"/>
-      <c r="N84" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K84" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="L84" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M84" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="N84" s="17" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A85" s="13"/>

--- a/vinit (2).xlsx
+++ b/vinit (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\776\12604409.xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68DE94AA-1379-41DB-90E8-71B1C561DFEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09BF74B4-22AB-4BBC-8A74-E4C9D5BB86E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="170">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4893,26 +4893,50 @@
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A85" s="13"/>
-      <c r="B85" s="14"/>
-      <c r="C85" s="14"/>
-      <c r="D85" s="14"/>
-      <c r="E85" s="14"/>
-      <c r="F85" s="14"/>
-      <c r="G85" s="14"/>
-      <c r="H85" s="14"/>
-      <c r="I85" s="15" t="str">
+      <c r="A85" s="13">
+        <v>46325</v>
+      </c>
+      <c r="B85" s="14">
+        <v>480</v>
+      </c>
+      <c r="C85" s="14">
+        <v>60</v>
+      </c>
+      <c r="D85" s="14">
+        <v>240</v>
+      </c>
+      <c r="E85" s="14">
+        <v>240</v>
+      </c>
+      <c r="F85" s="14">
+        <v>0</v>
+      </c>
+      <c r="G85" s="14">
+        <v>0</v>
+      </c>
+      <c r="H85" s="14">
+        <v>180</v>
+      </c>
+      <c r="I85" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J85" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J85" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K85" s="16"/>
-      <c r="L85" s="16"/>
-      <c r="M85" s="16"/>
-      <c r="N85" s="17"/>
+        <v>240</v>
+      </c>
+      <c r="K85" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="L85" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M85" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="N85" s="17" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A86" s="13"/>
